--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.65023</v>
+        <v>16.79559</v>
       </c>
       <c r="D2" t="n">
-        <v>17.08037</v>
+        <v>16.26166</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76793</v>
+        <v>16.69097</v>
       </c>
       <c r="F2" t="n">
-        <v>43.91123</v>
+        <v>42.71802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05017</v>
+        <v>0.05021</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84036</v>
+        <v>1.82821</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.03862</v>
+        <v>16.95647</v>
       </c>
       <c r="D3" t="n">
-        <v>16.33441</v>
+        <v>16.18416</v>
       </c>
       <c r="E3" t="n">
-        <v>16.53613</v>
+        <v>16.82654</v>
       </c>
       <c r="F3" t="n">
-        <v>42.12835</v>
+        <v>42.44123</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05097</v>
+        <v>0.0513</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83433</v>
+        <v>1.79827</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.7843</v>
+        <v>16.73645</v>
       </c>
       <c r="D4" t="n">
-        <v>16.45542</v>
+        <v>16.27612</v>
       </c>
       <c r="E4" t="n">
-        <v>16.62977</v>
+        <v>16.6493</v>
       </c>
       <c r="F4" t="n">
-        <v>41.46783</v>
+        <v>42.14031</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05009</v>
+        <v>0.05153</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80216</v>
+        <v>1.80449</v>
       </c>
     </row>
   </sheetData>
